--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\OneDrive\SEPLAG\2022\SPLOR\DCPPN\LeiOrcamentariaAnual\LOA\bancos\SISOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38632DD8-2CE4-4B3F-BFBC-2FE3D58419E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20C519FF-E939-455C-BAC2-C7A482DD0AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="150" windowWidth="21600" windowHeight="11145"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_REPASSE_RECURSOS" sheetId="1" r:id="rId1"/>
@@ -981,7 +981,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1104,7 +1104,7 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>60</v>
@@ -1116,7 +1116,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>103823</v>
+        <v>3785967</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1133,7 +1133,7 @@
         <v>10</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>60</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>3785967</v>
+        <v>103823</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1832,7 +1832,7 @@
         <v>4</v>
       </c>
       <c r="F29">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>3962577</v>
+        <v>55734880</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1861,7 +1861,7 @@
         <v>4</v>
       </c>
       <c r="F30">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>55734880</v>
+        <v>3962577</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1977,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>94000000</v>
+        <v>110000000</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2006,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>110000000</v>
+        <v>94000000</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2093,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>918328876</v>
+        <v>679805385</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2122,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -2131,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>679805385</v>
+        <v>918328876</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2151,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>7055561</v>
+        <v>6141488</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2180,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>6141488</v>
+        <v>7055561</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">

--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -1,43 +1,276 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_REPASSE_RECURSOS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BASE_REPASSE_RECURSOS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+  <si>
+    <t xml:space="preserve">Cód. UO Financiadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UO Financiadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cód. UO Beneficiada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UO Beneficiada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo de Despesa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor Transferido (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.773,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.953,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.725.265,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOTERIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283.360,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.851.070,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.500.004,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.666.102,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.795.372,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTITUTO ESTADUAL DE FLORESTAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.364.802,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">437.229,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.651,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.043.510,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.598.748,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.497.298,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDAÇÃO EZEQUIEL DIAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.860.199,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319.867.767,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.179.273,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.358.703,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.190.157,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE FAZENDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.300.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.984.254,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.066.345,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.696.149,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.429.523,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.092.118,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.639.997,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.636.985,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.672.268,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">687.479.332,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">909.028.598,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.233.016,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.600.037,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCURADORIA GERAL DE JUSTIÇA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.638.646,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.825.328,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.641.237,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.412.328,00</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,94 +278,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
@@ -182,10 +338,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -211,15 +363,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -245,6 +394,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -420,77 +570,51 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cód. UO Financiadora</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UO Financiadora</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cód. UO Beneficiada</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>UO Beneficiada</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo de Despesa</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>IPU</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>IAG</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Transferido (R$)</t>
-        </is>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>1011</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B2" t="s">
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>1501</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D2" t="s">
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -504,26 +628,22 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>81773</v>
+      <c r="I2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2011</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B3" t="s">
+        <v>12</v>
       </c>
       <c r="C3" t="n">
         <v>1501</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D3" t="s">
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -537,26 +657,22 @@
       <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>58953</v>
+      <c r="I3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2011</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B4" t="s">
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>1501</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D4" t="s">
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -570,26 +686,22 @@
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
-        <v>4725265</v>
+      <c r="I4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>2041</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>1501</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D5" t="s">
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -603,26 +715,22 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>283360</v>
+      <c r="I5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>2041</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B6" t="s">
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>4711</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D6" t="s">
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -636,26 +744,22 @@
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
-        <v>1851070</v>
+      <c r="I6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>2091</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
-        </is>
+      <c r="B7" t="s">
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>1371</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
-        </is>
+      <c r="D7" t="s">
+        <v>20</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -669,26 +773,22 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="n">
-        <v>12500004</v>
+      <c r="I7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>2091</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
-        </is>
+      <c r="B8" t="s">
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>1501</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D8" t="s">
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -702,26 +802,22 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="n">
-        <v>1666102</v>
+      <c r="I8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>2091</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
-        </is>
+      <c r="B9" t="s">
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>4711</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D9" t="s">
+        <v>17</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -735,26 +831,22 @@
       <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
-        <v>4795372</v>
+      <c r="I9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>2101</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
-        </is>
+      <c r="B10" t="s">
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>1501</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D10" t="s">
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -768,26 +860,22 @@
       <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="I10" t="n">
-        <v>2364802</v>
+      <c r="I10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>2101</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
-        </is>
+      <c r="B11" t="s">
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>4031</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D11" t="s">
+        <v>26</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -801,26 +889,22 @@
       <c r="H11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="n">
-        <v>120000</v>
+      <c r="I11" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>2121</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B12" t="s">
+        <v>28</v>
       </c>
       <c r="C12" t="n">
         <v>1501</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D12" t="s">
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -834,26 +918,22 @@
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="n">
-        <v>437229</v>
+      <c r="I12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>2121</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B13" t="s">
+        <v>28</v>
       </c>
       <c r="C13" t="n">
         <v>1501</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D13" t="s">
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -867,26 +947,22 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="n">
-        <v>19651</v>
+      <c r="I13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>2121</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B14" t="s">
+        <v>28</v>
       </c>
       <c r="C14" t="n">
         <v>4711</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D14" t="s">
+        <v>17</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -900,26 +976,22 @@
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="n">
-        <v>1043510</v>
+      <c r="I14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>2241</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
-        </is>
+      <c r="B15" t="s">
+        <v>32</v>
       </c>
       <c r="C15" t="n">
         <v>1501</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D15" t="s">
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
@@ -933,26 +1005,22 @@
       <c r="H15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="n">
-        <v>1598748</v>
+      <c r="I15" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>2251</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B16" t="s">
+        <v>34</v>
       </c>
       <c r="C16" t="n">
         <v>4711</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D16" t="s">
+        <v>17</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -966,26 +1034,22 @@
       <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="n">
-        <v>3497298</v>
+      <c r="I16" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>2261</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
-        </is>
+      <c r="B17" t="s">
+        <v>36</v>
       </c>
       <c r="C17" t="n">
         <v>4711</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D17" t="s">
+        <v>17</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -999,26 +1063,22 @@
       <c r="H17" t="n">
         <v>0</v>
       </c>
-      <c r="I17" t="n">
-        <v>30860199</v>
+      <c r="I17" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>2271</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B18" t="s">
+        <v>38</v>
       </c>
       <c r="C18" t="n">
         <v>4711</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D18" t="s">
+        <v>17</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1032,26 +1092,22 @@
       <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="n">
-        <v>319867767</v>
+      <c r="I18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>2321</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-        </is>
+      <c r="B19" t="s">
+        <v>40</v>
       </c>
       <c r="C19" t="n">
         <v>4711</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D19" t="s">
+        <v>17</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -1065,26 +1121,22 @@
       <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="n">
-        <v>23179273</v>
+      <c r="I19" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>2441</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B20" t="s">
+        <v>42</v>
       </c>
       <c r="C20" t="n">
         <v>1501</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D20" t="s">
+        <v>10</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
@@ -1098,26 +1150,22 @@
       <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="n">
-        <v>1358703</v>
+      <c r="I20" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>4031</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B21" t="s">
+        <v>26</v>
       </c>
       <c r="C21" t="n">
         <v>1501</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
-        </is>
+      <c r="D21" t="s">
+        <v>10</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
@@ -1131,26 +1179,22 @@
       <c r="H21" t="n">
         <v>0</v>
       </c>
-      <c r="I21" t="n">
-        <v>1190157</v>
+      <c r="I21" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>4111</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="B22" t="s">
+        <v>45</v>
       </c>
       <c r="C22" t="n">
         <v>1915</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-        </is>
+      <c r="D22" t="s">
+        <v>46</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
@@ -1164,26 +1208,22 @@
       <c r="H22" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="n">
-        <v>130000</v>
+      <c r="I22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>4381</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
+      <c r="B23" t="s">
+        <v>48</v>
       </c>
       <c r="C23" t="n">
         <v>1191</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
-        </is>
+      <c r="D23" t="s">
+        <v>49</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
@@ -1197,26 +1237,22 @@
       <c r="H23" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="n">
-        <v>1300000</v>
+      <c r="I23" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>4381</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
+      <c r="B24" t="s">
+        <v>48</v>
       </c>
       <c r="C24" t="n">
         <v>1251</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D24" t="s">
+        <v>51</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
@@ -1230,26 +1266,22 @@
       <c r="H24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
-        <v>15000000</v>
+      <c r="I24" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>4381</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
+      <c r="B25" t="s">
+        <v>48</v>
       </c>
       <c r="C25" t="n">
         <v>1301</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
-        </is>
+      <c r="D25" t="s">
+        <v>53</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -1263,26 +1295,22 @@
       <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="I25" t="n">
-        <v>6984254</v>
+      <c r="I25" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>4381</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
+      <c r="B26" t="s">
+        <v>48</v>
       </c>
       <c r="C26" t="n">
         <v>1301</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
-        </is>
+      <c r="D26" t="s">
+        <v>53</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
@@ -1296,26 +1324,22 @@
       <c r="H26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="n">
-        <v>11066345</v>
+      <c r="I26" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>4381</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
+      <c r="B27" t="s">
+        <v>48</v>
       </c>
       <c r="C27" t="n">
         <v>2301</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D27" t="s">
+        <v>56</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
@@ -1329,26 +1353,22 @@
       <c r="H27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="n">
-        <v>113696149</v>
+      <c r="I27" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>4381</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
+      <c r="B28" t="s">
+        <v>48</v>
       </c>
       <c r="C28" t="n">
         <v>2301</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D28" t="s">
+        <v>56</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
@@ -1362,26 +1382,22 @@
       <c r="H28" t="n">
         <v>0</v>
       </c>
-      <c r="I28" t="n">
-        <v>135429523</v>
+      <c r="I28" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>4381</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
+      <c r="B29" t="s">
+        <v>48</v>
       </c>
       <c r="C29" t="n">
         <v>4631</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
-        </is>
+      <c r="D29" t="s">
+        <v>59</v>
       </c>
       <c r="E29" t="n">
         <v>5</v>
@@ -1395,26 +1411,22 @@
       <c r="H29" t="n">
         <v>0</v>
       </c>
-      <c r="I29" t="n">
-        <v>141092118</v>
+      <c r="I29" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A30" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
       </c>
       <c r="C30" t="n">
         <v>1011</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D30" t="s">
+        <v>9</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1428,26 +1440,22 @@
       <c r="H30" t="n">
         <v>0</v>
       </c>
-      <c r="I30" t="n">
-        <v>102000000</v>
+      <c r="I30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A31" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B31" t="s">
+        <v>17</v>
       </c>
       <c r="C31" t="n">
         <v>1011</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D31" t="s">
+        <v>9</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1461,26 +1469,22 @@
       <c r="H31" t="n">
         <v>0</v>
       </c>
-      <c r="I31" t="n">
-        <v>124639997</v>
+      <c r="I31" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A32" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
       </c>
       <c r="C32" t="n">
         <v>1021</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D32" t="s">
+        <v>63</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1494,26 +1498,22 @@
       <c r="H32" t="n">
         <v>0</v>
       </c>
-      <c r="I32" t="n">
-        <v>96636985</v>
+      <c r="I32" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A33" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
       </c>
       <c r="C33" t="n">
         <v>1021</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D33" t="s">
+        <v>63</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1527,26 +1527,22 @@
       <c r="H33" t="n">
         <v>0</v>
       </c>
-      <c r="I33" t="n">
-        <v>98672268</v>
+      <c r="I33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A34" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
       </c>
       <c r="C34" t="n">
         <v>1031</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D34" t="s">
+        <v>66</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -1560,26 +1556,22 @@
       <c r="H34" t="n">
         <v>0</v>
       </c>
-      <c r="I34" t="n">
-        <v>687479332</v>
+      <c r="I34" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A35" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
       </c>
       <c r="C35" t="n">
         <v>1031</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D35" t="s">
+        <v>66</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -1593,26 +1585,22 @@
       <c r="H35" t="n">
         <v>0</v>
       </c>
-      <c r="I35" t="n">
-        <v>909028598</v>
+      <c r="I35" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A36" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
       </c>
       <c r="C36" t="n">
         <v>1051</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D36" t="s">
+        <v>69</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1626,26 +1614,22 @@
       <c r="H36" t="n">
         <v>0</v>
       </c>
-      <c r="I36" t="n">
-        <v>7233016</v>
+      <c r="I36" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A37" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B37" t="s">
+        <v>17</v>
       </c>
       <c r="C37" t="n">
         <v>1051</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D37" t="s">
+        <v>69</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1659,26 +1643,22 @@
       <c r="H37" t="n">
         <v>0</v>
       </c>
-      <c r="I37" t="n">
-        <v>9600037</v>
+      <c r="I37" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A38" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
       </c>
       <c r="C38" t="n">
         <v>1091</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
-        </is>
+      <c r="D38" t="s">
+        <v>72</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -1692,26 +1672,22 @@
       <c r="H38" t="n">
         <v>0</v>
       </c>
-      <c r="I38" t="n">
-        <v>323638646</v>
+      <c r="I38" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A39" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
       </c>
       <c r="C39" t="n">
         <v>1091</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
-        </is>
+      <c r="D39" t="s">
+        <v>72</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -1725,26 +1701,22 @@
       <c r="H39" t="n">
         <v>0</v>
       </c>
-      <c r="I39" t="n">
-        <v>218825328</v>
+      <c r="I39" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A40" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
       </c>
       <c r="C40" t="n">
         <v>1441</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D40" t="s">
+        <v>75</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -1758,26 +1730,22 @@
       <c r="H40" t="n">
         <v>0</v>
       </c>
-      <c r="I40" t="n">
-        <v>63641237</v>
+      <c r="I40" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="A41" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B41" t="s">
+        <v>17</v>
       </c>
       <c r="C41" t="n">
         <v>1441</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
-        </is>
+      <c r="D41" t="s">
+        <v>75</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -1791,11 +1759,12 @@
       <c r="H41" t="n">
         <v>0</v>
       </c>
-      <c r="I41" t="n">
-        <v>90412328</v>
+      <c r="I41" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -492,28 +492,28 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>79562</v>
+        <v>81773</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1031</v>
+        <v>2011</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4031</v>
+        <v>1501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>60</v>
@@ -525,7 +525,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>121661460</v>
+        <v>58953</v>
       </c>
     </row>
     <row r="4">
@@ -558,16 +558,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3785967</v>
+        <v>4725265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2011</v>
+        <v>2041</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>60</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>103823</v>
+        <v>283360</v>
       </c>
     </row>
     <row r="6">
@@ -604,15 +604,15 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>60</v>
@@ -624,31 +624,31 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>224433</v>
+        <v>1851070</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2041</v>
+        <v>2091</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4711</v>
+        <v>1371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -657,31 +657,31 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1813832</v>
+        <v>12500004</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2071</v>
+        <v>2091</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO DE AMPARO À PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>19629</v>
+        <v>1666102</v>
       </c>
     </row>
     <row r="9">
@@ -703,15 +703,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1371</v>
+        <v>4711</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>52</v>
@@ -723,16 +723,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>11000000</v>
+        <v>4795372</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -747,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -756,31 +756,31 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1292884</v>
+        <v>2364802</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4711</v>
+        <v>4031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -789,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4301526</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2101</v>
+        <v>2121</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -822,28 +822,28 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1797673</v>
+        <v>437229</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2101</v>
+        <v>2121</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4031</v>
+        <v>1501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
         <v>60</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>120000</v>
+        <v>19651</v>
       </c>
     </row>
     <row r="14">
@@ -868,15 +868,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>60</v>
@@ -888,31 +888,31 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>351880</v>
+        <v>1043510</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2121</v>
+        <v>2241</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -921,28 +921,28 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>959741</v>
+        <v>1598748</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2241</v>
+        <v>2251</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>60</v>
@@ -954,16 +954,16 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1063377</v>
+        <v>3497298</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -987,16 +987,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3262338</v>
+        <v>30860199</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
+          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1020,16 +1020,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>28302185</v>
+        <v>319867767</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2271</v>
+        <v>2321</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1053,31 +1053,31 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>282810306</v>
+        <v>23179273</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2321</v>
+        <v>2441</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1086,16 +1086,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>21269692</v>
+        <v>1358703</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2441</v>
+        <v>4031</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1110,7 +1110,7 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -1119,31 +1119,31 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1085577</v>
+        <v>1190157</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4031</v>
+        <v>4111</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1081</v>
+        <v>1915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ADVOCACIA GERAL DO ESTADO</t>
+          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1152,31 +1152,31 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>58110</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4031</v>
+        <v>4381</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1501</v>
+        <v>1191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1185,31 +1185,31 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>943436</v>
+        <v>1300000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4111</v>
+        <v>4381</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1915</v>
+        <v>1251</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -1218,40 +1218,40 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>160000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4111</v>
+        <v>4381</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4491</v>
+        <v>1301</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>15000</v>
+        <v>6984254</v>
       </c>
     </row>
     <row r="26">
@@ -1264,18 +1264,18 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1191</v>
+        <v>1301</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1300000</v>
+        <v>11066345</v>
       </c>
     </row>
     <row r="27">
@@ -1297,15 +1297,15 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1251</v>
+        <v>2301</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
         <v>83</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>15000000</v>
+        <v>113696149</v>
       </c>
     </row>
     <row r="28">
@@ -1330,15 +1330,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1301</v>
+        <v>2301</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE</t>
+          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
         <v>60</v>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>10190760</v>
+        <v>135429523</v>
       </c>
     </row>
     <row r="29">
@@ -1363,15 +1363,15 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2301</v>
+        <v>4631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
         <v>60</v>
@@ -1383,139 +1383,139 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>55734880</v>
+        <v>141092118</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4381</v>
+        <v>4711</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2301</v>
+        <v>1011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>3962577</v>
+        <v>102000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4381</v>
+        <v>4711</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2301</v>
+        <v>1011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>90898738</v>
+        <v>124639997</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4381</v>
+        <v>4711</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4631</v>
+        <v>1021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>42</v>
+      </c>
+      <c r="G32" t="n">
         <v>5</v>
       </c>
-      <c r="F32" t="n">
-        <v>60</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2</v>
-      </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>207576050</v>
+        <v>96636985</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4661</v>
+        <v>4711</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FUNDO DE ATIVOS IMOBILIÁRIOS DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4671</v>
+        <v>1021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDO DE INVESTIMENTOS IMOBILIÁRIOS DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>300251026</v>
+        <v>98672268</v>
       </c>
     </row>
     <row r="34">
@@ -1528,11 +1528,11 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1011</v>
+        <v>1031</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>110000000</v>
+        <v>687479332</v>
       </c>
     </row>
     <row r="35">
@@ -1561,11 +1561,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1011</v>
+        <v>1031</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>94000000</v>
+        <v>909028598</v>
       </c>
     </row>
     <row r="36">
@@ -1594,18 +1594,18 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1021</v>
+        <v>1051</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G36" t="n">
         <v>5</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>98244016</v>
+        <v>7233016</v>
       </c>
     </row>
     <row r="37">
@@ -1627,18 +1627,18 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1021</v>
+        <v>1051</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G37" t="n">
         <v>5</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>97416748</v>
+        <v>9600037</v>
       </c>
     </row>
     <row r="38">
@@ -1660,18 +1660,18 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1031</v>
+        <v>1091</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G38" t="n">
         <v>5</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>679805385</v>
+        <v>323638646</v>
       </c>
     </row>
     <row r="39">
@@ -1693,18 +1693,18 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1031</v>
+        <v>1091</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G39" t="n">
         <v>5</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>918328876</v>
+        <v>218825328</v>
       </c>
     </row>
     <row r="40">
@@ -1726,11 +1726,11 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1051</v>
+        <v>1441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>6141488</v>
+        <v>63641237</v>
       </c>
     </row>
     <row r="41">
@@ -1759,11 +1759,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1051</v>
+        <v>1441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1779,139 +1779,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>7055561</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1091</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>42</v>
-      </c>
-      <c r="G42" t="n">
-        <v>5</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>307052630</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1091</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>43</v>
-      </c>
-      <c r="G43" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>203231862</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1441</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>43</v>
-      </c>
-      <c r="G44" t="n">
-        <v>5</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>54992317</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1441</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>42</v>
-      </c>
-      <c r="G45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>77558519</v>
+        <v>90412328</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>124639997</v>
+        <v>123820000</v>
       </c>
     </row>
     <row r="32">
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>687479332</v>
+        <v>777479336</v>
       </c>
     </row>
     <row r="35">
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>909028598</v>
+        <v>1005834666</v>
       </c>
     </row>
     <row r="36">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>323638646</v>
+        <v>331458483</v>
       </c>
     </row>
     <row r="39">
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>218825328</v>
+        <v>224112640</v>
       </c>
     </row>
     <row r="40">

--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -497,26 +497,26 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2011</v>
+        <v>1051</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -525,31 +525,31 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>58953</v>
+        <v>9600038</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2011</v>
+        <v>1051</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -558,16 +558,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4725265</v>
+        <v>7233018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2041</v>
+        <v>2011</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>60</v>
@@ -591,28 +591,28 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>283360</v>
+        <v>58953</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2041</v>
+        <v>2011</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>60</v>
@@ -624,31 +624,31 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1851070</v>
+        <v>4725265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2091</v>
+        <v>2041</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1371</v>
+        <v>1501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -657,31 +657,31 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>12500004</v>
+        <v>283360</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2091</v>
+        <v>2041</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1666102</v>
+        <v>1851070</v>
       </c>
     </row>
     <row r="9">
@@ -703,15 +703,15 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4711</v>
+        <v>1371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>52</v>
@@ -723,16 +723,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4795372</v>
+        <v>12500004</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2101</v>
+        <v>2091</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -747,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -756,31 +756,31 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2364802</v>
+        <v>1666102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2101</v>
+        <v>2091</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4031</v>
+        <v>4711</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -789,16 +789,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>120000</v>
+        <v>4795372</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2121</v>
+        <v>2101</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -822,28 +822,28 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>437229</v>
+        <v>2364802</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2121</v>
+        <v>2101</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1501</v>
+        <v>4031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>60</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>19651</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="14">
@@ -868,15 +868,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>60</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1043510</v>
+        <v>437229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2241</v>
+        <v>2121</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -921,16 +921,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1598748</v>
+        <v>19651</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2251</v>
+        <v>2121</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -954,31 +954,31 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3497298</v>
+        <v>1043510</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2261</v>
+        <v>2241</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -987,16 +987,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>30860199</v>
+        <v>1598748</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2271</v>
+        <v>2251</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1020,16 +1020,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>319867767</v>
+        <v>3497298</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2321</v>
+        <v>2261</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1053,31 +1053,31 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>23179273</v>
+        <v>30860199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2441</v>
+        <v>2271</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1086,28 +1086,28 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1358703</v>
+        <v>319867767</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4031</v>
+        <v>2321</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>60</v>
@@ -1119,31 +1119,31 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1190157</v>
+        <v>23179273</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4111</v>
+        <v>2441</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
+          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1915</v>
+        <v>1501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1152,31 +1152,31 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>130000</v>
+        <v>1358703</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4381</v>
+        <v>4031</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1191</v>
+        <v>1501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1185,31 +1185,31 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1300000</v>
+        <v>1190157</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4381</v>
+        <v>4111</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1251</v>
+        <v>1915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>15000000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="25">
@@ -1231,18 +1231,18 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1301</v>
+        <v>1191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>6984254</v>
+        <v>1300000</v>
       </c>
     </row>
     <row r="26">
@@ -1264,18 +1264,18 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1301</v>
+        <v>1251</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>11066345</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="27">
@@ -1297,18 +1297,18 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2301</v>
+        <v>1301</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>113696149</v>
+        <v>6984254</v>
       </c>
     </row>
     <row r="28">
@@ -1330,11 +1330,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2301</v>
+        <v>1301</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>135429523</v>
+        <v>11066345</v>
       </c>
     </row>
     <row r="29">
@@ -1363,18 +1363,18 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4631</v>
+        <v>2301</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
@@ -1383,73 +1383,73 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>141092118</v>
+        <v>113696149</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4711</v>
+        <v>4381</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1011</v>
+        <v>2301</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>102000000</v>
+        <v>135429523</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4711</v>
+        <v>4381</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1011</v>
+        <v>4631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>123820000</v>
+        <v>141092118</v>
       </c>
     </row>
     <row r="32">
@@ -1462,11 +1462,11 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>96636985</v>
+        <v>102000000</v>
       </c>
     </row>
     <row r="33">
@@ -1495,11 +1495,11 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>98672268</v>
+        <v>123820000</v>
       </c>
     </row>
     <row r="34">
@@ -1528,11 +1528,11 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>777479336</v>
+        <v>108552329</v>
       </c>
     </row>
     <row r="35">
@@ -1561,11 +1561,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1005834666</v>
+        <v>101083596</v>
       </c>
     </row>
     <row r="36">
@@ -1594,18 +1594,18 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1051</v>
+        <v>1031</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G36" t="n">
         <v>5</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>7233016</v>
+        <v>1103569901</v>
       </c>
     </row>
     <row r="37">
@@ -1627,18 +1627,18 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1051</v>
+        <v>1031</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G37" t="n">
         <v>5</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>9600037</v>
+        <v>777479336</v>
       </c>
     </row>
     <row r="38">
@@ -1660,11 +1660,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1091</v>
+        <v>1051</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>331458483</v>
+        <v>9600038</v>
       </c>
     </row>
     <row r="39">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1091</v>
+        <v>1051</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>224112640</v>
+        <v>7233016</v>
       </c>
     </row>
     <row r="40">
@@ -1726,18 +1726,18 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1441</v>
+        <v>1091</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G40" t="n">
         <v>5</v>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>63641237</v>
+        <v>331458483</v>
       </c>
     </row>
     <row r="41">
@@ -1759,18 +1759,18 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1441</v>
+        <v>1091</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G41" t="n">
         <v>5</v>
@@ -1779,7 +1779,73 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>90412328</v>
+        <v>224112640</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1441</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>42</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>95066258</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1441</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>43</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>63641237</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -497,26 +497,26 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1051</v>
+        <v>2011</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -525,31 +525,31 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>9600038</v>
+        <v>58953</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1051</v>
+        <v>2011</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -558,16 +558,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7233018</v>
+        <v>4725265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2011</v>
+        <v>2041</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>60</v>
@@ -591,28 +591,28 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>58953</v>
+        <v>283360</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2011</v>
+        <v>2041</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>60</v>
@@ -624,28 +624,28 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4725265</v>
+        <v>1851070</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2041</v>
+        <v>2071</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO DE AMPARO À PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>60</v>
@@ -657,31 +657,31 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>283360</v>
+        <v>11485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2041</v>
+        <v>2091</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4711</v>
+        <v>1371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1851070</v>
+        <v>12500004</v>
       </c>
     </row>
     <row r="9">
@@ -703,11 +703,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1371</v>
+        <v>1501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>12500004</v>
+        <v>1666102</v>
       </c>
     </row>
     <row r="10">
@@ -736,15 +736,15 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>52</v>
@@ -756,31 +756,31 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1666102</v>
+        <v>4795372</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4795372</v>
+        <v>2364802</v>
       </c>
     </row>
     <row r="12">
@@ -802,11 +802,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1501</v>
+        <v>4031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -822,24 +822,24 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2364802</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2101</v>
+        <v>2121</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4031</v>
+        <v>1501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>120000</v>
+        <v>437229</v>
       </c>
     </row>
     <row r="14">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>60</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>437229</v>
+        <v>19651</v>
       </c>
     </row>
     <row r="15">
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>60</v>
@@ -921,31 +921,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>19651</v>
+        <v>1043510</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2121</v>
+        <v>2241</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -954,31 +954,31 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1043510</v>
+        <v>1598748</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2241</v>
+        <v>2251</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -987,16 +987,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1598748</v>
+        <v>3497298</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2251</v>
+        <v>2261</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1020,16 +1020,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3497298</v>
+        <v>30860199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
+          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1053,16 +1053,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>30860199</v>
+        <v>319867767</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2271</v>
+        <v>2321</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1086,31 +1086,31 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>319867767</v>
+        <v>23179273</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2321</v>
+        <v>2441</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -1119,16 +1119,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>23179273</v>
+        <v>1358703</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2441</v>
+        <v>4031</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1143,7 +1143,7 @@
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1152,31 +1152,31 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1358703</v>
+        <v>1190157</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4031</v>
+        <v>4111</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1501</v>
+        <v>1915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1185,31 +1185,31 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1190157</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4111</v>
+        <v>4381</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1915</v>
+        <v>1191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>130000</v>
+        <v>1300000</v>
       </c>
     </row>
     <row r="25">
@@ -1231,11 +1231,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1191</v>
+        <v>1251</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1300000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="26">
@@ -1264,18 +1264,18 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1251</v>
+        <v>1301</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>15000000</v>
+        <v>11066345</v>
       </c>
     </row>
     <row r="27">
@@ -1330,18 +1330,18 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1301</v>
+        <v>2301</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>11066345</v>
+        <v>113696149</v>
       </c>
     </row>
     <row r="29">
@@ -1374,7 +1374,7 @@
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>113696149</v>
+        <v>135429523</v>
       </c>
     </row>
     <row r="30">
@@ -1396,15 +1396,15 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2301</v>
+        <v>4631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
         <v>60</v>
@@ -1416,40 +1416,40 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>135429523</v>
+        <v>141092118</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4381</v>
+        <v>4711</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4631</v>
+        <v>1011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42</v>
+      </c>
+      <c r="G31" t="n">
         <v>5</v>
       </c>
-      <c r="F31" t="n">
-        <v>60</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2</v>
-      </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>141092118</v>
+        <v>102000000</v>
       </c>
     </row>
     <row r="32">
@@ -1473,7 +1473,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G32" t="n">
         <v>5</v>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>102000000</v>
+        <v>123820000</v>
       </c>
     </row>
     <row r="33">
@@ -1495,18 +1495,18 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G33" t="n">
         <v>5</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>123820000</v>
+        <v>101083596</v>
       </c>
     </row>
     <row r="34">
@@ -1561,18 +1561,18 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G35" t="n">
         <v>5</v>
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>101083596</v>
+        <v>777479336</v>
       </c>
     </row>
     <row r="36">
@@ -1627,11 +1627,11 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1031</v>
+        <v>1051</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>777479336</v>
+        <v>7233016</v>
       </c>
     </row>
     <row r="38">
@@ -1693,18 +1693,18 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1051</v>
+        <v>1091</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G39" t="n">
         <v>5</v>
@@ -1713,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>7233016</v>
+        <v>331458483</v>
       </c>
     </row>
     <row r="40">
@@ -1737,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G40" t="n">
         <v>5</v>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>331458483</v>
+        <v>224112640</v>
       </c>
     </row>
     <row r="41">
@@ -1759,11 +1759,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1091</v>
+        <v>1441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>224112640</v>
+        <v>63641237</v>
       </c>
     </row>
     <row r="42">
@@ -1813,39 +1813,6 @@
       </c>
       <c r="I42" t="n">
         <v>95066258</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1441</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>43</v>
-      </c>
-      <c r="G43" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>63641237</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -492,28 +492,28 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>81773</v>
+        <v>107068</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2011</v>
+        <v>1031</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1501</v>
+        <v>4031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>60</v>
@@ -525,16 +525,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>58953</v>
+        <v>88237413</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2011</v>
+        <v>1051</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -558,64 +558,64 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4725265</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2041</v>
+        <v>1271</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1501</v>
+        <v>3151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>EMPRESA MINEIRA DE COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>283360</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2041</v>
+        <v>1301</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4711</v>
+        <v>4631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -624,28 +624,28 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1851070</v>
+        <v>1114825</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2071</v>
+        <v>2011</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO DE AMPARO À PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>60</v>
@@ -657,31 +657,31 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11485</v>
+        <v>5582278</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2091</v>
+        <v>2041</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1371</v>
+        <v>1501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -690,31 +690,31 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>12500004</v>
+        <v>302203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2091</v>
+        <v>2041</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -723,16 +723,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1666102</v>
+        <v>1811411</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2091</v>
+        <v>2071</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDAÇÃO DE AMPARO À PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -747,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -756,31 +756,31 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4795372</v>
+        <v>13339</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2101</v>
+        <v>2091</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1501</v>
+        <v>1371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -789,31 +789,31 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2364802</v>
+        <v>12500010</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2101</v>
+        <v>2091</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4031</v>
+        <v>1501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -822,31 +822,31 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>120000</v>
+        <v>1812548</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2121</v>
+        <v>2091</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -855,28 +855,28 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>437229</v>
+        <v>4599592</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2121</v>
+        <v>2101</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1501</v>
+        <v>1401</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>60</v>
@@ -888,28 +888,28 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>19651</v>
+        <v>5371382</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2121</v>
+        <v>2101</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>60</v>
@@ -921,31 +921,31 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1043510</v>
+        <v>2793087</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2241</v>
+        <v>2101</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1501</v>
+        <v>4031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -954,28 +954,28 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1598748</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2251</v>
+        <v>2121</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4711</v>
+        <v>1251</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>60</v>
@@ -987,28 +987,28 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3497298</v>
+        <v>4516011</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2261</v>
+        <v>2121</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4711</v>
+        <v>1251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>60</v>
@@ -1020,28 +1020,28 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>30860199</v>
+        <v>104433989</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2271</v>
+        <v>2121</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4711</v>
+        <v>1401</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>60</v>
@@ -1053,28 +1053,28 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>319867767</v>
+        <v>61402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2321</v>
+        <v>2121</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4711</v>
+        <v>1401</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>60</v>
@@ -1086,16 +1086,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>23179273</v>
+        <v>837458</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2441</v>
+        <v>2121</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1110,7 +1110,7 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -1119,28 +1119,28 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1358703</v>
+        <v>455219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4031</v>
+        <v>2121</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>60</v>
@@ -1152,31 +1152,31 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1190157</v>
+        <v>770893</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4111</v>
+        <v>2241</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1915</v>
+        <v>1501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1185,31 +1185,31 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>130000</v>
+        <v>1645693</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4381</v>
+        <v>2251</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1191</v>
+        <v>4711</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -1218,31 +1218,31 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1300000</v>
+        <v>3991527</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4381</v>
+        <v>2261</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1251</v>
+        <v>4711</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
@@ -1251,28 +1251,28 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>15000000</v>
+        <v>30994923</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4381</v>
+        <v>2271</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1301</v>
+        <v>4711</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>60</v>
@@ -1284,28 +1284,28 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>11066345</v>
+        <v>160378471</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4381</v>
+        <v>2321</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1301</v>
+        <v>4711</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>60</v>
@@ -1317,31 +1317,31 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>6984254</v>
+        <v>24272540</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4381</v>
+        <v>2371</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2301</v>
+        <v>1501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
@@ -1350,31 +1350,31 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>113696149</v>
+        <v>202860</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4381</v>
+        <v>2441</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2301</v>
+        <v>1501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICAÇÕES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
@@ -1383,28 +1383,28 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>135429523</v>
+        <v>1364291</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4381</v>
+        <v>4031</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4631</v>
+        <v>1081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>ADVOCACIA GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
         <v>60</v>
@@ -1416,403 +1416,931 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>141092118</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4711</v>
+        <v>4031</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1011</v>
+        <v>1501</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>102000000</v>
+        <v>1368740</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4711</v>
+        <v>4111</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1011</v>
+        <v>1915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>123820000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4711</v>
+        <v>4291</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAÚDE</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1021</v>
+        <v>1451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE JUSTIÇA E SEGURANÇA PÚBLICA</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>101083596</v>
+        <v>1336774</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4711</v>
+        <v>4291</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAÚDE</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1021</v>
+        <v>1511</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>108552329</v>
+        <v>20758</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4711</v>
+        <v>4291</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAÚDE</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1031</v>
+        <v>2011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>777479336</v>
+        <v>9326709</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4711</v>
+        <v>4291</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAÚDE</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1031</v>
+        <v>2121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1103569901</v>
+        <v>110652</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4711</v>
+        <v>4291</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAÚDE</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1051</v>
+        <v>2261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>7233016</v>
+        <v>13849</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4711</v>
+        <v>4291</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAÚDE</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1051</v>
+        <v>2271</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>9600038</v>
+        <v>31102717</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4711</v>
+        <v>4291</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAÚDE</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1091</v>
+        <v>2311</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>331458483</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4711</v>
+        <v>4291</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAÚDE</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1091</v>
+        <v>2321</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>224112640</v>
+        <v>727204</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4711</v>
+        <v>4381</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1441</v>
+        <v>1191</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>63641237</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>4381</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1251</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>83</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>14642907</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4381</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>60</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>47046294</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4381</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="n">
+        <v>60</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4381</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="n">
+        <v>83</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>28040838</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4381</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4631</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>60</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>105699643</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
         <v>4711</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C47" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>43</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>120240000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>42</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>103400000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>42</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>103953792</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>43</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>111782853</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>42</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1217336584</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>43</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>810102294</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>43</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>7322510</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>42</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>9905734</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1091</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>43</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>242041652</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1091</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>42</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>357975162</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
         <v>1441</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
         <v>42</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G57" t="n">
         <v>5</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>95066258</v>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>93738515</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4711</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1441</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>43</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>65292305</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -492,31 +492,31 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>107068</v>
+        <v>103231</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1031</v>
+        <v>1301</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4031</v>
+        <v>4631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -525,16 +525,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>88237413</v>
+        <v>3372264</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1051</v>
+        <v>2011</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -558,64 +558,64 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>5880</v>
+        <v>6980303</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1271</v>
+        <v>2011</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3151</v>
+        <v>1941</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EMPRESA MINEIRA DE COMUNICAÇÃO</t>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1301</v>
+        <v>2041</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4631</v>
+        <v>1501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -624,28 +624,28 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1114825</v>
+        <v>307920</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2011</v>
+        <v>2041</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>60</v>
@@ -657,28 +657,28 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5582278</v>
+        <v>1776827</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2041</v>
+        <v>2071</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO DE AMPARO À PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>60</v>
@@ -690,31 +690,31 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>302203</v>
+        <v>16838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2041</v>
+        <v>2091</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4711</v>
+        <v>1371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -723,31 +723,31 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1811411</v>
+        <v>13000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2071</v>
+        <v>2091</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO DE AMPARO À PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>13339</v>
+        <v>1633636</v>
       </c>
     </row>
     <row r="11">
@@ -769,15 +769,15 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1371</v>
+        <v>4711</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>52</v>
@@ -789,31 +789,31 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>12500010</v>
+        <v>4859876</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1501</v>
+        <v>1401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -822,31 +822,31 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1812548</v>
+        <v>6682057</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2091</v>
+        <v>2101</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4599592</v>
+        <v>2015107</v>
       </c>
     </row>
     <row r="14">
@@ -868,11 +868,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1401</v>
+        <v>4031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -888,24 +888,24 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5371382</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2101</v>
+        <v>2121</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1501</v>
+        <v>1251</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -921,28 +921,28 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2793087</v>
+        <v>134472993</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2101</v>
+        <v>2121</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4031</v>
+        <v>1251</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>120000</v>
+        <v>9754107</v>
       </c>
     </row>
     <row r="17">
@@ -967,15 +967,15 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1251</v>
+        <v>1401</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
         <v>60</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4516011</v>
+        <v>822699</v>
       </c>
     </row>
     <row r="18">
@@ -1000,15 +1000,15 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1251</v>
+        <v>1401</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>60</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>104433989</v>
+        <v>48202</v>
       </c>
     </row>
     <row r="19">
@@ -1033,15 +1033,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1401</v>
+        <v>1501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>60</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>61402</v>
+        <v>12444</v>
       </c>
     </row>
     <row r="20">
@@ -1066,15 +1066,15 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1401</v>
+        <v>4711</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>60</v>
@@ -1086,16 +1086,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>837458</v>
+        <v>884722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2121</v>
+        <v>2241</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1119,16 +1119,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>455219</v>
+        <v>1381549</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2121</v>
+        <v>2251</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1152,31 +1152,31 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>770893</v>
+        <v>4207639</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2241</v>
+        <v>2261</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
+          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1645693</v>
+        <v>32737210</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2251</v>
+        <v>2271</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3991527</v>
+        <v>235218509</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2261</v>
+        <v>2321</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
+          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1251,31 +1251,31 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>30994923</v>
+        <v>27341045</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2271</v>
+        <v>2371</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
@@ -1284,31 +1284,31 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>160378471</v>
+        <v>221046</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2321</v>
+        <v>2441</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -1317,24 +1317,24 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>24272540</v>
+        <v>1290973</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2371</v>
+        <v>4031</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTIÇA E SEGURANÇA PÚBLICA</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1350,40 +1350,40 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>202860</v>
+        <v>875221853</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2441</v>
+        <v>4031</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTIÇA E SEGURANÇA PÚBLICA</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1364291</v>
+        <v>1778147</v>
       </c>
     </row>
     <row r="30">
@@ -1396,11 +1396,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1081</v>
+        <v>1501</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ADVOCACIA GERAL DO ESTADO</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1416,31 +1416,31 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>48000</v>
+        <v>1318193</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4031</v>
+        <v>4111</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1501</v>
+        <v>1915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
@@ -1449,31 +1449,31 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1368740</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4111</v>
+        <v>4291</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAÚDE</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1915</v>
+        <v>1451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>SECRETARIA DE ESTADO DE JUSTIÇA E SEGURANÇA PÚBLICA</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>110000</v>
+        <v>1138967</v>
       </c>
     </row>
     <row r="33">
@@ -1495,11 +1495,11 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1451</v>
+        <v>1511</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTIÇA E SEGURANÇA PÚBLICA</t>
+          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1336774</v>
+        <v>13543</v>
       </c>
     </row>
     <row r="34">
@@ -1528,11 +1528,11 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1511</v>
+        <v>2011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1548,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>20758</v>
+        <v>7356625</v>
       </c>
     </row>
     <row r="35">
@@ -1561,11 +1561,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2011</v>
+        <v>2121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>9326709</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="36">
@@ -1594,11 +1594,11 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2121</v>
+        <v>2261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>110652</v>
+        <v>13845</v>
       </c>
     </row>
     <row r="37">
@@ -1627,11 +1627,11 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
+          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>13849</v>
+        <v>32667892</v>
       </c>
     </row>
     <row r="38">
@@ -1660,11 +1660,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2271</v>
+        <v>2311</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>31102717</v>
+        <v>1794000</v>
       </c>
     </row>
     <row r="39">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2311</v>
+        <v>2321</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1718,26 +1718,26 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4291</v>
+        <v>4381</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2321</v>
+        <v>1191</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>727204</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="41">
@@ -1759,11 +1759,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1191</v>
+        <v>1251</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>900000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="42">
@@ -1792,18 +1792,18 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1251</v>
+        <v>2471</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>14642907</v>
+        <v>2001130</v>
       </c>
     </row>
     <row r="43">
@@ -1825,11 +1825,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1301</v>
+        <v>2471</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>47046294</v>
+        <v>37635820</v>
       </c>
     </row>
     <row r="44">
@@ -1858,15 +1858,15 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1301</v>
+        <v>4631</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
         <v>60</v>
@@ -1878,73 +1878,73 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1400000</v>
+        <v>60788935</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4381</v>
+        <v>4491</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2301</v>
+        <v>3151</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>28040838</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4381</v>
+        <v>4711</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4631</v>
+        <v>1011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>43</v>
+      </c>
+      <c r="G46" t="n">
         <v>5</v>
       </c>
-      <c r="F46" t="n">
-        <v>60</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
-      </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>105699643</v>
+        <v>126400000</v>
       </c>
     </row>
     <row r="47">
@@ -1968,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G47" t="n">
         <v>5</v>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>120240000</v>
+        <v>112000000</v>
       </c>
     </row>
     <row r="48">
@@ -1990,11 +1990,11 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>103400000</v>
+        <v>104407495</v>
       </c>
     </row>
     <row r="49">
@@ -2034,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G49" t="n">
         <v>5</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>103953792</v>
+        <v>118906754</v>
       </c>
     </row>
     <row r="50">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>111782853</v>
+        <v>891570030</v>
       </c>
     </row>
     <row r="51">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1217336584</v>
+        <v>1081813774</v>
       </c>
     </row>
     <row r="52">
@@ -2122,11 +2122,11 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1031</v>
+        <v>1051</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>810102294</v>
+        <v>9665367</v>
       </c>
     </row>
     <row r="53">
@@ -2166,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G53" t="n">
         <v>5</v>
@@ -2175,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>7322510</v>
+        <v>9851943</v>
       </c>
     </row>
     <row r="54">
@@ -2188,11 +2188,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1051</v>
+        <v>1091</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>9905734</v>
+        <v>391082727</v>
       </c>
     </row>
     <row r="55">
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>242041652</v>
+        <v>260748891</v>
       </c>
     </row>
     <row r="56">
@@ -2254,11 +2254,11 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1091</v>
+        <v>1441</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>357975162</v>
+        <v>101210335</v>
       </c>
     </row>
     <row r="57">
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G57" t="n">
         <v>5</v>
@@ -2307,40 +2307,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>93738515</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1441</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" t="n">
-        <v>43</v>
-      </c>
-      <c r="G58" t="n">
-        <v>5</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>65292305</v>
+        <v>67978647</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -464,92 +464,92 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1011</v>
+        <v>4711</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1501</v>
+        <v>1091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>103231</v>
+        <v>300411652</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1301</v>
+        <v>4711</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4631</v>
+        <v>1091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3372264</v>
+        <v>448050447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2011</v>
+        <v>4381</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1501</v>
+        <v>1191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -558,214 +558,214 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6980303</v>
+        <v>1008000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2011</v>
+        <v>4711</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1941</v>
+        <v>1021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>100000</v>
+        <v>133292078</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2041</v>
+        <v>4711</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1501</v>
+        <v>1021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>307920</v>
+        <v>115233552</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2041</v>
+        <v>4711</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4711</v>
+        <v>1051</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1776827</v>
+        <v>8800648</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2071</v>
+        <v>4711</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO DE AMPARO À PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4711</v>
+        <v>1051</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>16838</v>
+        <v>11045990</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2091</v>
+        <v>4711</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1371</v>
+        <v>1011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>13000000</v>
+        <v>129510000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2091</v>
+        <v>4711</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1501</v>
+        <v>1011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1633636</v>
+        <v>120000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2091</v>
+        <v>2261</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -780,7 +780,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -789,31 +789,31 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4859876</v>
+        <v>34739894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2101</v>
+        <v>1301</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1401</v>
+        <v>4631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -822,28 +822,28 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>6682057</v>
+        <v>727000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2101</v>
+        <v>4381</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1501</v>
+        <v>2471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
         <v>60</v>
@@ -855,24 +855,24 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2015107</v>
+        <v>17964220</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2101</v>
+        <v>4381</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4031</v>
+        <v>2471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -888,31 +888,31 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>120000</v>
+        <v>5780000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2121</v>
+        <v>2371</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1251</v>
+        <v>1501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -921,28 +921,28 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>134472993</v>
+        <v>149161</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2121</v>
+        <v>2091</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1251</v>
+        <v>4711</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>9754107</v>
+        <v>155090</v>
       </c>
     </row>
     <row r="17">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>60</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>822699</v>
+        <v>575076</v>
       </c>
     </row>
     <row r="18">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>60</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>48202</v>
+        <v>1004919</v>
       </c>
     </row>
     <row r="19">
@@ -1033,18 +1033,18 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1501</v>
+        <v>1251</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>12444</v>
+        <v>15642001</v>
       </c>
     </row>
     <row r="20">
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4711</v>
+        <v>1251</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1086,16 +1086,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>884722</v>
+        <v>140778004</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2241</v>
+        <v>2121</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1119,31 +1119,31 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1381549</v>
+        <v>107449</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2251</v>
+        <v>2091</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1152,31 +1152,31 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4207639</v>
+        <v>2177178</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2261</v>
+        <v>2091</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4711</v>
+        <v>1371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1185,31 +1185,31 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>32737210</v>
+        <v>13650000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2271</v>
+        <v>2241</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>235218509</v>
+        <v>1774713</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2321</v>
+        <v>2041</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1251,16 +1251,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>27341045</v>
+        <v>1686000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2371</v>
+        <v>2041</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1275,7 +1275,7 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>221046</v>
+        <v>458582</v>
       </c>
     </row>
     <row r="27">
@@ -1317,28 +1317,28 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1290973</v>
+        <v>1707737</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4031</v>
+        <v>2251</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1451</v>
+        <v>4711</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTIÇA E SEGURANÇA PÚBLICA</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>60</v>
@@ -1350,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>875221853</v>
+        <v>4444845</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4031</v>
+        <v>2321</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1451</v>
+        <v>4711</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTIÇA E SEGURANÇA PÚBLICA</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>60</v>
@@ -1380,19 +1380,19 @@
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1778147</v>
+        <v>31836274</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4031</v>
+        <v>2101</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1407,7 +1407,7 @@
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -1416,31 +1416,31 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1318193</v>
+        <v>3110043</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4111</v>
+        <v>4031</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1915</v>
+        <v>1501</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
@@ -1449,31 +1449,31 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>110000</v>
+        <v>1570548</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4291</v>
+        <v>4031</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1451</v>
+        <v>1081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTIÇA E SEGURANÇA PÚBLICA</t>
+          <t>ADVOCACIA GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -1482,31 +1482,31 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1138967</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4291</v>
+        <v>4381</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1511</v>
+        <v>1251</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>POLÍCIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
@@ -1515,64 +1515,64 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>13543</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4291</v>
+        <v>1271</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2011</v>
+        <v>4491</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>16</v>
+      </c>
+      <c r="G34" t="n">
         <v>1</v>
       </c>
-      <c r="F34" t="n">
-        <v>57</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2</v>
-      </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>7356625</v>
+        <v>130003000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4291</v>
+        <v>2011</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2121</v>
+        <v>1941</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
@@ -1581,31 +1581,31 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>70000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4291</v>
+        <v>2011</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2261</v>
+        <v>1501</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G36" t="n">
         <v>2</v>
@@ -1614,31 +1614,31 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>13845</v>
+        <v>6311890</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4291</v>
+        <v>1011</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2271</v>
+        <v>1501</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
@@ -1647,31 +1647,31 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>32667892</v>
+        <v>104706</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4291</v>
+        <v>4111</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAÚDE</t>
+          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2311</v>
+        <v>1915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
@@ -1680,634 +1680,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1794000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>4291</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE SAÚDE</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2321</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>57</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>4381</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1191</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" t="n">
-        <v>83</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>960000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>4381</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>1251</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" t="n">
-        <v>83</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>15000000</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>4381</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2471</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" t="n">
-        <v>60</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2001130</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>4381</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2471</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" t="n">
-        <v>60</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>37635820</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>4381</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>4631</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>5</v>
-      </c>
-      <c r="F44" t="n">
-        <v>60</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>60788935</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>4491</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>3151</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>EMPRESA MINEIRA DE COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" t="n">
-        <v>59</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1011</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>43</v>
-      </c>
-      <c r="G46" t="n">
-        <v>5</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>126400000</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1011</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G47" t="n">
-        <v>5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>112000000</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1021</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>42</v>
-      </c>
-      <c r="G48" t="n">
-        <v>5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>104407495</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1021</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>43</v>
-      </c>
-      <c r="G49" t="n">
-        <v>5</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>118906754</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1031</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>43</v>
-      </c>
-      <c r="G50" t="n">
-        <v>5</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>891570030</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1031</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>42</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1081813774</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1051</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" t="n">
-        <v>43</v>
-      </c>
-      <c r="G52" t="n">
-        <v>5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>9665367</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1051</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>42</v>
-      </c>
-      <c r="G53" t="n">
-        <v>5</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>9851943</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1091</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" t="n">
-        <v>42</v>
-      </c>
-      <c r="G54" t="n">
-        <v>5</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>391082727</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1091</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>43</v>
-      </c>
-      <c r="G55" t="n">
-        <v>5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>260748891</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1441</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>42</v>
-      </c>
-      <c r="G56" t="n">
-        <v>5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>101210335</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>4711</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1441</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>43</v>
-      </c>
-      <c r="G57" t="n">
-        <v>5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>67978647</v>
+        <v>98000</v>
       </c>
     </row>
   </sheetData>

--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -472,11 +472,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1091</v>
+        <v>1031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -492,106 +492,106 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>300411652</v>
+        <v>880513540</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4711</v>
+        <v>4491</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1091</v>
+        <v>2201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMÔNIO HISTÓRICO E ARTÍSTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>448050447</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4381</v>
+        <v>4491</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1191</v>
+        <v>2171</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>FUNDAÇÃO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1008000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4711</v>
+        <v>4491</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1021</v>
+        <v>2181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO CLÓVIS SALGADO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>133292078</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>115233552</v>
+        <v>1131169707</v>
       </c>
     </row>
     <row r="7">
@@ -637,11 +637,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1051</v>
+        <v>1441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>8800648</v>
+        <v>72184243</v>
       </c>
     </row>
     <row r="8">
@@ -670,11 +670,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1051</v>
+        <v>1441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -690,40 +690,40 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>11045990</v>
+        <v>105515757</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4711</v>
+        <v>2101</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1011</v>
+        <v>1401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>129510000</v>
+        <v>7016160</v>
       </c>
     </row>
     <row r="10">
@@ -736,18 +736,18 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1011</v>
+        <v>1091</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
         <v>5</v>
@@ -756,64 +756,64 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>120000000</v>
+        <v>300411652</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2261</v>
+        <v>4711</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4711</v>
+        <v>1091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTIÇA</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>34739894</v>
+        <v>448050447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1301</v>
+        <v>4381</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4631</v>
+        <v>1191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
@@ -822,229 +822,229 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>727000</v>
+        <v>1008000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4381</v>
+        <v>4711</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2471</v>
+        <v>1021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>17964220</v>
+        <v>133292078</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4381</v>
+        <v>4711</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2471</v>
+        <v>1021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5780000</v>
+        <v>115233552</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2371</v>
+        <v>4711</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1501</v>
+        <v>1051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>149161</v>
+        <v>8800648</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2091</v>
+        <v>4711</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4711</v>
+        <v>1051</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTIÇA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>155090</v>
+        <v>11045990</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2121</v>
+        <v>4711</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1401</v>
+        <v>1011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>575076</v>
+        <v>129510000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2121</v>
+        <v>4711</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1401</v>
+        <v>1011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1004919</v>
+        <v>120000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2121</v>
+        <v>2261</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1251</v>
+        <v>4711</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
@@ -1053,31 +1053,31 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>15642001</v>
+        <v>34739894</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2121</v>
+        <v>1301</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1251</v>
+        <v>4631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PÚBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1086,28 +1086,28 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>140778004</v>
+        <v>727000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2121</v>
+        <v>4381</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1501</v>
+        <v>2471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>60</v>
@@ -1119,31 +1119,31 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>107449</v>
+        <v>17964220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2091</v>
+        <v>4381</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1501</v>
+        <v>2471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>AGÊNCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1152,31 +1152,31 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2177178</v>
+        <v>5780000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2091</v>
+        <v>2371</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUÁRIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1371</v>
+        <v>1501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1185,31 +1185,31 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>13650000</v>
+        <v>149161</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2241</v>
+        <v>2091</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -1218,28 +1218,28 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1774713</v>
+        <v>155090</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2041</v>
+        <v>2121</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4711</v>
+        <v>1401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>60</v>
@@ -1251,24 +1251,24 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1686000</v>
+        <v>575076</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2041</v>
+        <v>2121</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1501</v>
+        <v>1401</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1284,31 +1284,31 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>458582</v>
+        <v>1004919</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2441</v>
+        <v>2121</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1501</v>
+        <v>1251</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -1317,31 +1317,31 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1707737</v>
+        <v>15642001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2251</v>
+        <v>2121</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4711</v>
+        <v>1251</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
@@ -1350,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>4444845</v>
+        <v>140778004</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2321</v>
+        <v>2121</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4711</v>
+        <v>1501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
         <v>60</v>
@@ -1383,16 +1383,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>31836274</v>
+        <v>107449</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2101</v>
+        <v>2091</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1416,31 +1416,31 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>3110043</v>
+        <v>2177178</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4031</v>
+        <v>2091</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1501</v>
+        <v>1371</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTÁVEL</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
@@ -1449,31 +1449,31 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1570548</v>
+        <v>13650000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4031</v>
+        <v>2241</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTÃO DAS ÁGUAS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1081</v>
+        <v>1501</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ADVOCACIA GERAL DO ESTADO</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -1482,31 +1482,31 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>45000</v>
+        <v>1774713</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4381</v>
+        <v>2041</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1251</v>
+        <v>4711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G33" t="n">
         <v>2</v>
@@ -1515,64 +1515,64 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>15000000</v>
+        <v>1686000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1271</v>
+        <v>2041</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4491</v>
+        <v>1501</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>130003000</v>
+        <v>458582</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2011</v>
+        <v>2441</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>AGÊNCIA REGULADORA DE SERVIÇOS DE ABASTECIMENTO DE ÁGUA E DE ESGOTAMENTO SANITÁRIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1941</v>
+        <v>1501</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
@@ -1581,28 +1581,28 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>150000</v>
+        <v>1707737</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2011</v>
+        <v>2251</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>60</v>
@@ -1614,28 +1614,28 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>6311890</v>
+        <v>4444845</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1011</v>
+        <v>2321</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDAÇÃO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1501</v>
+        <v>4711</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDÊNCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>60</v>
@@ -1647,39 +1647,303 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>104706</v>
+        <v>31836274</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>91</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3110043</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4031</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>60</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1570548</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4031</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FUNDO ESPECIAL DO PODER JUDICIÁRIO DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1081</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ADVOCACIA GERAL DO ESTADO</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>60</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4381</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1251</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>POLÍCIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>83</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4491</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>16</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>130003000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1941</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>60</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="n">
+        <v>60</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6311890</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>60</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>104706</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
         <v>4111</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C46" t="n">
         <v>1915</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E46" t="n">
         <v>5</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F46" t="n">
         <v>61</v>
       </c>
-      <c r="G38" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>98000</v>
       </c>
     </row>

--- a/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
+++ b/bancos/SISOR/BASE_REPASSE_RECURSOS.xlsx
@@ -1784,35 +1784,35 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1271</v>
+        <v>2011</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4491</v>
+        <v>1941</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>130003000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="43">
@@ -1825,11 +1825,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1941</v>
+        <v>1501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1845,16 +1845,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>150000</v>
+        <v>6311890</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2011</v>
+        <v>1011</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDÊNCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1878,31 +1878,31 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>6311890</v>
+        <v>104706</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1011</v>
+        <v>4111</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1501</v>
+        <v>1915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO</t>
+          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
@@ -1911,39 +1911,6 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>104706</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>4111</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>FUNDO DE FOMENTO E DESENVOLVIMENTO SOCIOECONÔMICO DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1915</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>PARTICIPAÇÃO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F46" t="n">
-        <v>61</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
         <v>98000</v>
       </c>
     </row>
